--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["tabs-minimal"]</t>
+    <t>["hero-intro","columns-feature","cards-gallery","tabs-testimonial","cards-article","accordion-faq","hero-banner"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,13 +52,13 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-29T14:44:40.424Z</t>
-  </si>
-  <si>
-    <t>About</t>
-  </si>
-  <si>
-    <t>https://www.dianalefebvre.ca/</t>
+    <t>2026-07-29T18:00:38.833Z</t>
+  </si>
+  <si>
+    <t>WKND Trendsetters - Fresh Looks, Bold Stories, Real Life</t>
+  </si>
+  <si>
+    <t>https://www.wknd-trendsetters.site/</t>
   </si>
 </sst>
 </file>
@@ -451,12 +451,12 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-29T18:00:38.833Z</t>
+    <t>2026-07-30T13:36:40.649Z</t>
   </si>
   <si>
     <t>WKND Trendsetters - Fresh Looks, Bold Stories, Real Life</t>
